--- a/datos_y_modelos/Domestic/domestic_sovereign_curve_brazil.xlsx
+++ b/datos_y_modelos/Domestic/domestic_sovereign_curve_brazil.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsiqueira4\Downloads\spread-model-master\light_spread-model-master\datos_y_modelos\Domestic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA68573-8AD5-4924-8A30-0A583257DA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CEF396-2321-48ED-88FF-28E086A778BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="18470" windowHeight="12220" xr2:uid="{4FA8D609-CF7D-453F-9379-B1555420C1B0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{4FA8D609-CF7D-453F-9379-B1555420C1B0}"/>
   </bookViews>
   <sheets>
     <sheet name="db_values_only" sheetId="1" r:id="rId1"/>
@@ -1050,7 +1050,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1060,6 +1060,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1077,13 +1083,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3324,7 +3331,7 @@
       <c r="M2">
         <v>712</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="4" t="s">
         <v>208</v>
       </c>
       <c r="O2" t="s">
@@ -3437,7 +3444,7 @@
       <c r="M3">
         <v>1171</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O3" t="s">
@@ -3550,7 +3557,7 @@
       <c r="M4">
         <v>712</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="4" t="s">
         <v>208</v>
       </c>
       <c r="O4" t="s">
@@ -3663,7 +3670,7 @@
       <c r="M5">
         <v>712</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="4" t="s">
         <v>208</v>
       </c>
       <c r="O5" t="s">
@@ -3776,7 +3783,7 @@
       <c r="M6">
         <v>1171</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O6" t="s">
@@ -3889,7 +3896,7 @@
       <c r="M7">
         <v>712</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="4" t="s">
         <v>208</v>
       </c>
       <c r="O7" t="s">
@@ -4002,7 +4009,7 @@
       <c r="M8">
         <v>712</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="4" t="s">
         <v>208</v>
       </c>
       <c r="O8" t="s">
@@ -4115,7 +4122,7 @@
       <c r="M9">
         <v>1193</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="4" t="s">
         <v>235</v>
       </c>
       <c r="O9" t="s">
@@ -4228,7 +4235,7 @@
       <c r="M10">
         <v>1171</v>
       </c>
-      <c r="N10" t="s">
+      <c r="N10" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O10" t="s">
@@ -4341,7 +4348,7 @@
       <c r="M11">
         <v>712</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N11" s="4" t="s">
         <v>208</v>
       </c>
       <c r="O11" t="s">
@@ -4454,7 +4461,7 @@
       <c r="M12">
         <v>1309</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N12" s="4" t="s">
         <v>242</v>
       </c>
       <c r="O12" t="s">
@@ -4567,7 +4574,7 @@
       <c r="M13">
         <v>1171</v>
       </c>
-      <c r="N13" t="s">
+      <c r="N13" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O13" t="s">
@@ -4680,7 +4687,7 @@
       <c r="M14">
         <v>712</v>
       </c>
-      <c r="N14" t="s">
+      <c r="N14" s="4" t="s">
         <v>208</v>
       </c>
       <c r="O14" t="s">
@@ -4793,7 +4800,7 @@
       <c r="M15">
         <v>1193</v>
       </c>
-      <c r="N15" t="s">
+      <c r="N15" s="4" t="s">
         <v>235</v>
       </c>
       <c r="O15" t="s">
@@ -4906,7 +4913,7 @@
       <c r="M16">
         <v>712</v>
       </c>
-      <c r="N16" t="s">
+      <c r="N16" s="4" t="s">
         <v>208</v>
       </c>
       <c r="O16" t="s">
@@ -5019,7 +5026,7 @@
       <c r="M17">
         <v>1171</v>
       </c>
-      <c r="N17" t="s">
+      <c r="N17" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O17" t="s">
@@ -5132,7 +5139,7 @@
       <c r="M18">
         <v>712</v>
       </c>
-      <c r="N18" t="s">
+      <c r="N18" s="4" t="s">
         <v>208</v>
       </c>
       <c r="O18" t="s">
@@ -5245,7 +5252,7 @@
       <c r="M19">
         <v>1171</v>
       </c>
-      <c r="N19" t="s">
+      <c r="N19" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O19" t="s">
@@ -5358,7 +5365,7 @@
       <c r="M20">
         <v>712</v>
       </c>
-      <c r="N20" t="s">
+      <c r="N20" s="4" t="s">
         <v>208</v>
       </c>
       <c r="O20" t="s">
@@ -5471,7 +5478,7 @@
       <c r="M21">
         <v>1193</v>
       </c>
-      <c r="N21" t="s">
+      <c r="N21" s="4" t="s">
         <v>235</v>
       </c>
       <c r="O21" t="s">
@@ -5584,7 +5591,7 @@
       <c r="M22">
         <v>1171</v>
       </c>
-      <c r="N22" t="s">
+      <c r="N22" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O22" t="s">
@@ -5697,7 +5704,7 @@
       <c r="M23">
         <v>1309</v>
       </c>
-      <c r="N23" t="s">
+      <c r="N23" s="4" t="s">
         <v>242</v>
       </c>
       <c r="O23" t="s">
@@ -5810,7 +5817,7 @@
       <c r="M24">
         <v>712</v>
       </c>
-      <c r="N24" t="s">
+      <c r="N24" s="4" t="s">
         <v>208</v>
       </c>
       <c r="O24" t="s">
@@ -5923,7 +5930,7 @@
       <c r="M25">
         <v>1171</v>
       </c>
-      <c r="N25" t="s">
+      <c r="N25" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O25" t="s">
@@ -6036,7 +6043,7 @@
       <c r="M26">
         <v>1193</v>
       </c>
-      <c r="N26" t="s">
+      <c r="N26" s="4" t="s">
         <v>235</v>
       </c>
       <c r="O26" t="s">
@@ -6149,7 +6156,7 @@
       <c r="M27">
         <v>1171</v>
       </c>
-      <c r="N27" t="s">
+      <c r="N27" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O27" t="s">
@@ -6262,7 +6269,7 @@
       <c r="M28">
         <v>712</v>
       </c>
-      <c r="N28" t="s">
+      <c r="N28" s="4" t="s">
         <v>208</v>
       </c>
       <c r="O28" t="s">
@@ -6375,7 +6382,7 @@
       <c r="M29">
         <v>1171</v>
       </c>
-      <c r="N29" t="s">
+      <c r="N29" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O29" t="s">
@@ -6488,7 +6495,7 @@
       <c r="M30">
         <v>1171</v>
       </c>
-      <c r="N30" t="s">
+      <c r="N30" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O30" t="s">
@@ -6601,7 +6608,7 @@
       <c r="M31">
         <v>1193</v>
       </c>
-      <c r="N31" t="s">
+      <c r="N31" s="4" t="s">
         <v>235</v>
       </c>
       <c r="O31" t="s">
@@ -6714,7 +6721,7 @@
       <c r="M32">
         <v>1171</v>
       </c>
-      <c r="N32" t="s">
+      <c r="N32" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O32" t="s">
@@ -6827,7 +6834,7 @@
       <c r="M33">
         <v>1171</v>
       </c>
-      <c r="N33" t="s">
+      <c r="N33" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O33" t="s">
@@ -6940,7 +6947,7 @@
       <c r="M34">
         <v>1195</v>
       </c>
-      <c r="N34" t="s">
+      <c r="N34" s="4" t="s">
         <v>235</v>
       </c>
       <c r="O34" t="s">
@@ -7053,7 +7060,7 @@
       <c r="M35">
         <v>1309</v>
       </c>
-      <c r="N35" t="s">
+      <c r="N35" s="4" t="s">
         <v>242</v>
       </c>
       <c r="O35" t="s">
@@ -7166,7 +7173,7 @@
       <c r="M36">
         <v>1171</v>
       </c>
-      <c r="N36" t="s">
+      <c r="N36" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O36" t="s">
@@ -7279,7 +7286,7 @@
       <c r="M37">
         <v>1171</v>
       </c>
-      <c r="N37" t="s">
+      <c r="N37" s="4" t="s">
         <v>222</v>
       </c>
       <c r="O37" t="s">
@@ -7392,7 +7399,7 @@
       <c r="M38">
         <v>712</v>
       </c>
-      <c r="N38" t="s">
+      <c r="N38" s="4" t="s">
         <v>208</v>
       </c>
       <c r="O38" t="s">
@@ -7505,7 +7512,7 @@
       <c r="M39">
         <v>1193</v>
       </c>
-      <c r="N39" t="s">
+      <c r="N39" s="4" t="s">
         <v>235</v>
       </c>
       <c r="O39" t="s">
@@ -7618,7 +7625,7 @@
       <c r="M40">
         <v>1309</v>
       </c>
-      <c r="N40" t="s">
+      <c r="N40" s="4" t="s">
         <v>242</v>
       </c>
       <c r="O40" t="s">
@@ -7731,7 +7738,7 @@
       <c r="M41">
         <v>1193</v>
       </c>
-      <c r="N41" t="s">
+      <c r="N41" s="4" t="s">
         <v>235</v>
       </c>
       <c r="O41" t="s">
@@ -7844,7 +7851,7 @@
       <c r="M42">
         <v>1309</v>
       </c>
-      <c r="N42" t="s">
+      <c r="N42" s="4" t="s">
         <v>242</v>
       </c>
       <c r="O42" t="s">
@@ -7957,7 +7964,7 @@
       <c r="M43">
         <v>1193</v>
       </c>
-      <c r="N43" t="s">
+      <c r="N43" s="4" t="s">
         <v>235</v>
       </c>
       <c r="O43" t="s">
@@ -8070,7 +8077,7 @@
       <c r="M44">
         <v>1193</v>
       </c>
-      <c r="N44" t="s">
+      <c r="N44" s="4" t="s">
         <v>235</v>
       </c>
       <c r="O44" t="s">
@@ -8183,7 +8190,7 @@
       <c r="M45">
         <v>1193</v>
       </c>
-      <c r="N45" t="s">
+      <c r="N45" s="4" t="s">
         <v>235</v>
       </c>
       <c r="O45" t="s">
@@ -8296,7 +8303,7 @@
       <c r="M46">
         <v>1193</v>
       </c>
-      <c r="N46" t="s">
+      <c r="N46" s="4" t="s">
         <v>235</v>
       </c>
       <c r="O46" t="s">
@@ -8409,7 +8416,7 @@
       <c r="M47">
         <v>1193</v>
       </c>
-      <c r="N47" t="s">
+      <c r="N47" s="4" t="s">
         <v>235</v>
       </c>
       <c r="O47" t="s">
@@ -8522,7 +8529,7 @@
       <c r="M48">
         <v>1193</v>
       </c>
-      <c r="N48" t="s">
+      <c r="N48" s="4" t="s">
         <v>235</v>
       </c>
       <c r="O48" t="s">

--- a/datos_y_modelos/Domestic/domestic_sovereign_curve_brazil.xlsx
+++ b/datos_y_modelos/Domestic/domestic_sovereign_curve_brazil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsiqueira4\Downloads\spread-model-master\light_spread-model-master\datos_y_modelos\Domestic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CEF396-2321-48ED-88FF-28E086A778BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898FAF1D-956C-407B-BCF6-210B844C475F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{4FA8D609-CF7D-453F-9379-B1555420C1B0}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">db_values_only!$C$1:$N$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">db_values_only!$A$1:$AK$47</definedName>
     <definedName name="_INH">'[1]Estimates Break Down'!$Y$1</definedName>
     <definedName name="bb_Mzk0MjlDQUYwQjg5NEJCM0" hidden="1">#REF!</definedName>
     <definedName name="bb_RjdDN0M0MkE1NDhCNEQyNj" hidden="1">#REF!</definedName>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="296">
   <si>
     <t>ISSUER</t>
   </si>
@@ -286,15 +286,6 @@
     <t>3/1/2029</t>
   </si>
   <si>
-    <t>BRSTNCNTC0K4</t>
-  </si>
-  <si>
-    <t>1/2/2001</t>
-  </si>
-  <si>
-    <t>7/1/2001</t>
-  </si>
-  <si>
     <t>BRSTNCNTB0A6</t>
   </si>
   <si>
@@ -619,9 +610,6 @@
     <t>BRSTNCLF1RT8 Corp</t>
   </si>
   <si>
-    <t>BRSTNCNTC0K4 Corp</t>
-  </si>
-  <si>
     <t>BRSTNCNTF204 Corp</t>
   </si>
   <si>
@@ -944,9 +932,6 @@
   </si>
   <si>
     <t>BBG01KWP4PM9</t>
-  </si>
-  <si>
-    <t>BBG000045TR2</t>
   </si>
   <si>
     <t>1/1/2031</t>
@@ -3158,7 +3143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A970A97D-4899-4477-842A-DD8D42C7E015}">
-  <dimension ref="A1:AK58"/>
+  <dimension ref="A1:AK57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
@@ -3180,16 +3165,16 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -3201,7 +3186,7 @@
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -3210,7 +3195,7 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>6</v>
@@ -3219,90 +3204,90 @@
         <v>7</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>182</v>
+      </c>
+      <c r="R1" t="s">
         <v>183</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>186</v>
-      </c>
-      <c r="R1" t="s">
-        <v>187</v>
       </c>
       <c r="S1" t="s">
         <v>8</v>
       </c>
       <c r="T1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="U1" t="s">
         <v>9</v>
       </c>
       <c r="V1" t="s">
+        <v>185</v>
+      </c>
+      <c r="W1" t="s">
+        <v>186</v>
+      </c>
+      <c r="X1" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z1" t="s">
         <v>189</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AA1" t="s">
         <v>190</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AB1" t="s">
         <v>191</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AC1" t="s">
         <v>192</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>194</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>195</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>196</v>
       </c>
       <c r="AD1" t="s">
         <v>10</v>
       </c>
       <c r="AE1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>194</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>195</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI1" t="s">
         <v>197</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AJ1" t="s">
         <v>198</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AK1" t="s">
         <v>199</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>200</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>202</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C2" t="s">
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -3311,10 +3296,10 @@
         <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I2" t="s">
         <v>34</v>
@@ -3323,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L2" t="s">
         <v>15</v>
@@ -3332,58 +3317,58 @@
         <v>712</v>
       </c>
       <c r="N2" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="O2" t="s">
+        <v>203</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>205</v>
+      </c>
+      <c r="R2" t="s">
+        <v>206</v>
+      </c>
+      <c r="S2" t="s">
+        <v>203</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="U2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V2" t="s">
+        <v>205</v>
+      </c>
+      <c r="W2" t="s">
+        <v>205</v>
+      </c>
+      <c r="X2" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y2" t="s">
         <v>208</v>
       </c>
-      <c r="O2" t="s">
-        <v>207</v>
-      </c>
-      <c r="P2" s="3" t="s">
+      <c r="Z2" t="s">
         <v>209</v>
       </c>
-      <c r="Q2" t="s">
-        <v>209</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="AA2" t="s">
         <v>210</v>
       </c>
-      <c r="S2" t="s">
-        <v>207</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="U2" t="s">
-        <v>209</v>
-      </c>
-      <c r="V2" t="s">
-        <v>209</v>
-      </c>
-      <c r="W2" t="s">
-        <v>209</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="AB2" t="s">
         <v>211</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AC2" t="s">
         <v>212</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AD2" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE2" t="s">
         <v>213</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>217</v>
       </c>
       <c r="AF2">
         <v>114346544000</v>
@@ -3392,30 +3377,30 @@
         <v>0</v>
       </c>
       <c r="AH2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
@@ -3427,7 +3412,7 @@
         <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I3" t="s">
         <v>34</v>
@@ -3436,7 +3421,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -3445,58 +3430,58 @@
         <v>1171</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>205</v>
+      </c>
+      <c r="R3" t="s">
+        <v>206</v>
+      </c>
+      <c r="S3" t="s">
+        <v>203</v>
+      </c>
+      <c r="T3" t="s">
+        <v>205</v>
+      </c>
+      <c r="U3" t="s">
+        <v>205</v>
+      </c>
+      <c r="V3" t="s">
+        <v>205</v>
+      </c>
+      <c r="W3" t="s">
+        <v>205</v>
+      </c>
+      <c r="X3" t="s">
         <v>207</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Y3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z3" t="s">
         <v>209</v>
       </c>
-      <c r="Q3" t="s">
-        <v>209</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="AA3" t="s">
         <v>210</v>
       </c>
-      <c r="S3" t="s">
-        <v>207</v>
-      </c>
-      <c r="T3" t="s">
-        <v>209</v>
-      </c>
-      <c r="U3" t="s">
-        <v>209</v>
-      </c>
-      <c r="V3" t="s">
-        <v>209</v>
-      </c>
-      <c r="W3" t="s">
-        <v>209</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="AB3" t="s">
         <v>211</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AC3" t="s">
         <v>212</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AD3" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE3" t="s">
         <v>213</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>217</v>
       </c>
       <c r="AF3">
         <v>249029080000</v>
@@ -3505,42 +3490,42 @@
         <v>0</v>
       </c>
       <c r="AH3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I4" t="s">
         <v>34</v>
@@ -3549,7 +3534,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -3558,58 +3543,58 @@
         <v>712</v>
       </c>
       <c r="N4" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="O4" t="s">
+        <v>203</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>205</v>
+      </c>
+      <c r="R4" t="s">
+        <v>206</v>
+      </c>
+      <c r="S4" t="s">
+        <v>203</v>
+      </c>
+      <c r="T4" t="s">
+        <v>205</v>
+      </c>
+      <c r="U4" t="s">
+        <v>205</v>
+      </c>
+      <c r="V4" t="s">
+        <v>205</v>
+      </c>
+      <c r="W4" t="s">
+        <v>205</v>
+      </c>
+      <c r="X4" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y4" t="s">
         <v>208</v>
       </c>
-      <c r="O4" t="s">
-        <v>207</v>
-      </c>
-      <c r="P4" s="3" t="s">
+      <c r="Z4" t="s">
         <v>209</v>
       </c>
-      <c r="Q4" t="s">
-        <v>209</v>
-      </c>
-      <c r="R4" t="s">
+      <c r="AA4" t="s">
         <v>210</v>
       </c>
-      <c r="S4" t="s">
-        <v>207</v>
-      </c>
-      <c r="T4" t="s">
-        <v>209</v>
-      </c>
-      <c r="U4" t="s">
-        <v>209</v>
-      </c>
-      <c r="V4" t="s">
-        <v>209</v>
-      </c>
-      <c r="W4" t="s">
-        <v>209</v>
-      </c>
-      <c r="X4" t="s">
+      <c r="AB4" t="s">
         <v>211</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="AC4" t="s">
         <v>212</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AD4" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE4" t="s">
         <v>213</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>217</v>
       </c>
       <c r="AF4">
         <v>115806750000</v>
@@ -3618,30 +3603,30 @@
         <v>0</v>
       </c>
       <c r="AH4" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
         <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E5" t="s">
         <v>49</v>
@@ -3650,10 +3635,10 @@
         <v>50</v>
       </c>
       <c r="G5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H5" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I5" t="s">
         <v>34</v>
@@ -3662,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -3671,22 +3656,22 @@
         <v>712</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="O5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q5" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T5">
         <v>92.169999999999959</v>
@@ -3701,28 +3686,28 @@
         <v>66800</v>
       </c>
       <c r="X5" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB5" t="s">
         <v>211</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="AC5" t="s">
         <v>212</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AD5" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE5" t="s">
         <v>213</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>217</v>
       </c>
       <c r="AF5">
         <v>173545554000</v>
@@ -3731,30 +3716,30 @@
         <v>173545554000</v>
       </c>
       <c r="AH5" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ5" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E6" t="s">
         <v>25</v>
@@ -3766,7 +3751,7 @@
         <v>27</v>
       </c>
       <c r="H6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I6" t="s">
         <v>34</v>
@@ -3775,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -3784,22 +3769,22 @@
         <v>1171</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T6">
         <v>-1396.42</v>
@@ -3814,28 +3799,28 @@
         <v>480000</v>
       </c>
       <c r="X6" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB6" t="s">
         <v>211</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="AC6" t="s">
         <v>212</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AD6" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE6" t="s">
         <v>213</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>217</v>
       </c>
       <c r="AF6">
         <v>328692760000</v>
@@ -3844,42 +3829,42 @@
         <v>328692760000</v>
       </c>
       <c r="AH6" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK6" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I7" t="s">
         <v>34</v>
@@ -3888,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L7" t="s">
         <v>15</v>
@@ -3897,22 +3882,22 @@
         <v>712</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="O7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q7" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T7">
         <v>72.559999999999832</v>
@@ -3924,31 +3909,31 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
+        <v>205</v>
+      </c>
+      <c r="X7" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z7" t="s">
         <v>209</v>
       </c>
-      <c r="X7" t="s">
+      <c r="AA7" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB7" t="s">
         <v>211</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="AC7" t="s">
         <v>212</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AD7" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE7" t="s">
         <v>213</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>217</v>
       </c>
       <c r="AF7">
         <v>115841186000</v>
@@ -3957,42 +3942,42 @@
         <v>115841186000</v>
       </c>
       <c r="AH7" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ7" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK7" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H8" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I8" t="s">
         <v>34</v>
@@ -4001,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L8" t="s">
         <v>15</v>
@@ -4010,22 +3995,22 @@
         <v>712</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="O8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R8" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T8">
         <v>41.17999999999995</v>
@@ -4040,28 +4025,28 @@
         <v>60000</v>
       </c>
       <c r="X8" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB8" t="s">
         <v>211</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="AC8" t="s">
         <v>212</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AD8" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE8" t="s">
         <v>213</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>217</v>
       </c>
       <c r="AF8">
         <v>198785456000</v>
@@ -4070,42 +4055,42 @@
         <v>198785456000</v>
       </c>
       <c r="AH8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ8" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK8" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H9" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I9" t="s">
         <v>14</v>
@@ -4114,7 +4099,7 @@
         <v>6</v>
       </c>
       <c r="K9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L9" t="s">
         <v>19</v>
@@ -4123,19 +4108,19 @@
         <v>1193</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="R9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S9">
         <v>2</v>
@@ -4153,28 +4138,28 @@
         <v>112609</v>
       </c>
       <c r="X9" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB9" t="s">
         <v>211</v>
       </c>
-      <c r="Y9" t="s">
+      <c r="AC9" t="s">
         <v>212</v>
       </c>
-      <c r="Z9" t="s">
+      <c r="AD9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE9" t="s">
         <v>213</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>217</v>
       </c>
       <c r="AF9">
         <v>226052038000</v>
@@ -4183,42 +4168,42 @@
         <v>226052038000</v>
       </c>
       <c r="AH9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s">
         <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H10" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I10" t="s">
         <v>34</v>
@@ -4227,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L10" t="s">
         <v>15</v>
@@ -4236,22 +4221,22 @@
         <v>1171</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O10" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S10" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T10">
         <v>-1397.33</v>
@@ -4266,28 +4251,28 @@
         <v>251236</v>
       </c>
       <c r="X10" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB10" t="s">
         <v>211</v>
       </c>
-      <c r="Y10" t="s">
+      <c r="AC10" t="s">
         <v>212</v>
       </c>
-      <c r="Z10" t="s">
+      <c r="AD10" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE10" t="s">
         <v>213</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>217</v>
       </c>
       <c r="AF10">
         <v>160319420000</v>
@@ -4296,42 +4281,42 @@
         <v>160319420000</v>
       </c>
       <c r="AH10" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI10" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ10" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK10" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G11" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H11" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I11" t="s">
         <v>34</v>
@@ -4340,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L11" t="s">
         <v>15</v>
@@ -4349,22 +4334,22 @@
         <v>712</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="O11" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q11" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R11" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S11" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T11">
         <v>-1.000000000015433E-2</v>
@@ -4376,31 +4361,31 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
+        <v>205</v>
+      </c>
+      <c r="X11" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z11" t="s">
         <v>209</v>
       </c>
-      <c r="X11" t="s">
+      <c r="AA11" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB11" t="s">
         <v>211</v>
       </c>
-      <c r="Y11" t="s">
+      <c r="AC11" t="s">
         <v>212</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="AD11" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE11" t="s">
         <v>213</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>217</v>
       </c>
       <c r="AF11">
         <v>48752778000</v>
@@ -4409,42 +4394,42 @@
         <v>48752778000</v>
       </c>
       <c r="AH11" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI11" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ11" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK11" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G12" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H12" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I12" t="s">
         <v>14</v>
@@ -4453,7 +4438,7 @@
         <v>10</v>
       </c>
       <c r="K12" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L12" t="s">
         <v>15</v>
@@ -4462,19 +4447,19 @@
         <v>1309</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="O12" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q12" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="R12" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S12">
         <v>2</v>
@@ -4492,28 +4477,28 @@
         <v>1732161</v>
       </c>
       <c r="X12" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB12" t="s">
         <v>211</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="AC12" t="s">
         <v>212</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="AD12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE12" t="s">
         <v>213</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>76</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>217</v>
       </c>
       <c r="AF12">
         <v>110474759000</v>
@@ -4522,42 +4507,42 @@
         <v>110474759000</v>
       </c>
       <c r="AH12" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI12" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ12" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK12" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I13" t="s">
         <v>34</v>
@@ -4566,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L13" t="s">
         <v>15</v>
@@ -4575,22 +4560,22 @@
         <v>1171</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O13" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q13" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R13" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S13" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T13">
         <v>-1356.1112739726027</v>
@@ -4605,28 +4590,28 @@
         <v>273149</v>
       </c>
       <c r="X13" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB13" t="s">
         <v>211</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="AC13" t="s">
         <v>212</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="AD13" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE13" t="s">
         <v>213</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>217</v>
       </c>
       <c r="AF13">
         <v>520324775000</v>
@@ -4635,42 +4620,42 @@
         <v>520324775000</v>
       </c>
       <c r="AH13" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI13" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ13" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK13" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G14" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H14" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I14" t="s">
         <v>34</v>
@@ -4679,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L14" t="s">
         <v>15</v>
@@ -4688,22 +4673,22 @@
         <v>712</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="O14" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q14" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R14" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S14" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T14">
         <v>-10.695972602739623</v>
@@ -4715,31 +4700,31 @@
         <v>0</v>
       </c>
       <c r="W14" t="s">
+        <v>205</v>
+      </c>
+      <c r="X14" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z14" t="s">
         <v>209</v>
       </c>
-      <c r="X14" t="s">
+      <c r="AA14" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB14" t="s">
         <v>211</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="AC14" t="s">
         <v>212</v>
       </c>
-      <c r="Z14" t="s">
+      <c r="AD14" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE14" t="s">
         <v>213</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>217</v>
       </c>
       <c r="AF14">
         <v>76582436000</v>
@@ -4748,30 +4733,30 @@
         <v>76582436000</v>
       </c>
       <c r="AH14" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI14" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ14" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK14" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E15" t="s">
         <v>42</v>
@@ -4780,10 +4765,10 @@
         <v>43</v>
       </c>
       <c r="G15" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H15" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I15" t="s">
         <v>14</v>
@@ -4792,7 +4777,7 @@
         <v>6</v>
       </c>
       <c r="K15" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L15" t="s">
         <v>19</v>
@@ -4801,19 +4786,19 @@
         <v>1193</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O15" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q15" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R15" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S15">
         <v>2</v>
@@ -4828,31 +4813,31 @@
         <v>0</v>
       </c>
       <c r="W15" t="s">
+        <v>205</v>
+      </c>
+      <c r="X15" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z15" t="s">
         <v>209</v>
       </c>
-      <c r="X15" t="s">
+      <c r="AA15" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB15" t="s">
         <v>211</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="AC15" t="s">
         <v>212</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>213</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>216</v>
       </c>
       <c r="AD15" t="s">
         <v>44</v>
       </c>
       <c r="AE15" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AF15">
         <v>121814271000</v>
@@ -4861,42 +4846,42 @@
         <v>121814271000</v>
       </c>
       <c r="AH15" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI15" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ15" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK15" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B16" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E16" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G16" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H16" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I16" t="s">
         <v>34</v>
@@ -4905,7 +4890,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L16" t="s">
         <v>15</v>
@@ -4914,22 +4899,22 @@
         <v>712</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="O16" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q16" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R16" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S16" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T16">
         <v>-9.6539589041096718</v>
@@ -4944,28 +4929,28 @@
         <v>100000</v>
       </c>
       <c r="X16" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB16" t="s">
         <v>211</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="AC16" t="s">
         <v>212</v>
       </c>
-      <c r="Z16" t="s">
+      <c r="AD16" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE16" t="s">
         <v>213</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>217</v>
       </c>
       <c r="AF16">
         <v>93083525000</v>
@@ -4974,30 +4959,30 @@
         <v>93083525000</v>
       </c>
       <c r="AH16" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI16" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ16" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK16" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B17" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C17" t="s">
         <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -5009,7 +4994,7 @@
         <v>30</v>
       </c>
       <c r="H17" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I17" t="s">
         <v>34</v>
@@ -5018,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L17" t="s">
         <v>15</v>
@@ -5027,22 +5012,22 @@
         <v>1171</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O17" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q17" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R17" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S17" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T17">
         <v>-1307.5133561643838</v>
@@ -5057,28 +5042,28 @@
         <v>75240</v>
       </c>
       <c r="X17" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB17" t="s">
         <v>211</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="AC17" t="s">
         <v>212</v>
       </c>
-      <c r="Z17" t="s">
+      <c r="AD17" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE17" t="s">
         <v>213</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>217</v>
       </c>
       <c r="AF17">
         <v>446613830000</v>
@@ -5087,42 +5072,42 @@
         <v>446613830000</v>
       </c>
       <c r="AH17" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI17" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ17" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK17" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E18" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H18" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I18" t="s">
         <v>34</v>
@@ -5131,7 +5116,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L18" t="s">
         <v>15</v>
@@ -5140,22 +5125,22 @@
         <v>712</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="O18" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q18" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S18" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T18">
         <v>-12.988449781659384</v>
@@ -5170,28 +5155,28 @@
         <v>70000</v>
       </c>
       <c r="X18" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB18" t="s">
         <v>211</v>
       </c>
-      <c r="Y18" t="s">
+      <c r="AC18" t="s">
         <v>212</v>
       </c>
-      <c r="Z18" t="s">
+      <c r="AD18" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE18" t="s">
         <v>213</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>217</v>
       </c>
       <c r="AF18">
         <v>56260077000</v>
@@ -5200,30 +5185,30 @@
         <v>56260077000</v>
       </c>
       <c r="AH18" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI18" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ18" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK18" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B19" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C19" t="s">
         <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E19" t="s">
         <v>35</v>
@@ -5235,7 +5220,7 @@
         <v>37</v>
       </c>
       <c r="H19" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I19" t="s">
         <v>34</v>
@@ -5244,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L19" t="s">
         <v>15</v>
@@ -5253,22 +5238,22 @@
         <v>1171</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O19" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q19" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R19" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S19" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T19">
         <v>-1294.5159170305681</v>
@@ -5283,28 +5268,28 @@
         <v>50000</v>
       </c>
       <c r="X19" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB19" t="s">
         <v>211</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="AC19" t="s">
         <v>212</v>
       </c>
-      <c r="Z19" t="s">
+      <c r="AD19" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE19" t="s">
         <v>213</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>217</v>
       </c>
       <c r="AF19">
         <v>306753014000</v>
@@ -5313,42 +5298,42 @@
         <v>306753014000</v>
       </c>
       <c r="AH19" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI19" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ19" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK19" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
       </c>
       <c r="D20" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E20" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G20" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H20" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I20" t="s">
         <v>34</v>
@@ -5357,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L20" t="s">
         <v>15</v>
@@ -5366,22 +5351,22 @@
         <v>712</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="O20" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q20" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R20" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S20" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T20">
         <v>-14.668100436681186</v>
@@ -5396,28 +5381,28 @@
         <v>30000</v>
       </c>
       <c r="X20" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB20" t="s">
         <v>211</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="AC20" t="s">
         <v>212</v>
       </c>
-      <c r="Z20" t="s">
+      <c r="AD20" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE20" t="s">
         <v>213</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>217</v>
       </c>
       <c r="AF20">
         <v>20973925000</v>
@@ -5426,30 +5411,30 @@
         <v>20973925000</v>
       </c>
       <c r="AH20" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI20" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ20" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK20" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B21" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E21" t="s">
         <v>17</v>
@@ -5458,10 +5443,10 @@
         <v>18</v>
       </c>
       <c r="G21" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I21" t="s">
         <v>14</v>
@@ -5470,7 +5455,7 @@
         <v>6</v>
       </c>
       <c r="K21" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L21" t="s">
         <v>19</v>
@@ -5479,19 +5464,19 @@
         <v>1193</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O21" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q21" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R21" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S21">
         <v>2</v>
@@ -5509,28 +5494,28 @@
         <v>50000</v>
       </c>
       <c r="X21" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB21" t="s">
         <v>211</v>
       </c>
-      <c r="Y21" t="s">
+      <c r="AC21" t="s">
         <v>212</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>213</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>216</v>
       </c>
       <c r="AD21" t="s">
         <v>20</v>
       </c>
       <c r="AE21" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AF21">
         <v>213887531000</v>
@@ -5539,30 +5524,30 @@
         <v>213887531000</v>
       </c>
       <c r="AH21" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI21" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ21" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK21" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E22" t="s">
         <v>46</v>
@@ -5574,7 +5559,7 @@
         <v>48</v>
       </c>
       <c r="H22" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I22" t="s">
         <v>34</v>
@@ -5583,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L22" t="s">
         <v>15</v>
@@ -5592,22 +5577,22 @@
         <v>1171</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O22" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q22" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R22" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S22" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T22">
         <v>-1288.512816593887</v>
@@ -5622,28 +5607,28 @@
         <v>25000</v>
       </c>
       <c r="X22" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB22" t="s">
         <v>211</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="AC22" t="s">
         <v>212</v>
       </c>
-      <c r="Z22" t="s">
+      <c r="AD22" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE22" t="s">
         <v>213</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE22" t="s">
-        <v>217</v>
       </c>
       <c r="AF22">
         <v>298922107000</v>
@@ -5652,30 +5637,30 @@
         <v>298922107000</v>
       </c>
       <c r="AH22" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI22" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ22" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK22" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
@@ -5684,10 +5669,10 @@
         <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H23" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I23" t="s">
         <v>14</v>
@@ -5696,7 +5681,7 @@
         <v>10</v>
       </c>
       <c r="K23" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L23" t="s">
         <v>15</v>
@@ -5705,19 +5690,19 @@
         <v>1309</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="O23" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q23" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R23" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S23">
         <v>2</v>
@@ -5735,28 +5720,28 @@
         <v>258000</v>
       </c>
       <c r="X23" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB23" t="s">
         <v>211</v>
       </c>
-      <c r="Y23" t="s">
+      <c r="AC23" t="s">
         <v>212</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>213</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC23" t="s">
-        <v>216</v>
       </c>
       <c r="AD23" t="s">
         <v>16</v>
       </c>
       <c r="AE23" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AF23">
         <v>114107909000</v>
@@ -5765,42 +5750,42 @@
         <v>114107909000</v>
       </c>
       <c r="AH23" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI23" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ23" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK23" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C24" t="s">
         <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E24" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H24" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I24" t="s">
         <v>34</v>
@@ -5809,7 +5794,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L24" t="s">
         <v>15</v>
@@ -5818,22 +5803,22 @@
         <v>712</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="O24" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q24" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R24" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S24" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T24">
         <v>-5.0000000001659828E-3</v>
@@ -5848,28 +5833,28 @@
         <v>629000</v>
       </c>
       <c r="X24" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB24" t="s">
         <v>211</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="AC24" t="s">
         <v>212</v>
       </c>
-      <c r="Z24" t="s">
+      <c r="AD24" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE24" t="s">
         <v>213</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>217</v>
       </c>
       <c r="AF24">
         <v>172702108000</v>
@@ -5878,30 +5863,30 @@
         <v>172702108000</v>
       </c>
       <c r="AH24" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI24" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ24" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK24" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C25" t="s">
         <v>21</v>
       </c>
       <c r="D25" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E25" t="s">
         <v>51</v>
@@ -5913,7 +5898,7 @@
         <v>53</v>
       </c>
       <c r="H25" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I25" t="s">
         <v>34</v>
@@ -5922,7 +5907,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L25" t="s">
         <v>15</v>
@@ -5931,22 +5916,22 @@
         <v>1171</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O25" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q25" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R25" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S25" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T25">
         <v>-1287.0810000000001</v>
@@ -5958,31 +5943,31 @@
         <v>0</v>
       </c>
       <c r="W25" t="s">
+        <v>205</v>
+      </c>
+      <c r="X25" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z25" t="s">
         <v>209</v>
       </c>
-      <c r="X25" t="s">
+      <c r="AA25" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB25" t="s">
         <v>211</v>
       </c>
-      <c r="Y25" t="s">
+      <c r="AC25" t="s">
         <v>212</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="AD25" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE25" t="s">
         <v>213</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB25" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC25" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE25" t="s">
-        <v>217</v>
       </c>
       <c r="AF25">
         <v>334130478000</v>
@@ -5991,42 +5976,42 @@
         <v>334130478000</v>
       </c>
       <c r="AH25" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI25" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ25" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK25" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B26" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E26" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="H26" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I26" t="s">
         <v>14</v>
@@ -6035,7 +6020,7 @@
         <v>6</v>
       </c>
       <c r="K26" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L26" t="s">
         <v>19</v>
@@ -6044,19 +6029,19 @@
         <v>1193</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O26" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q26" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R26" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S26">
         <v>2</v>
@@ -6071,31 +6056,31 @@
         <v>0</v>
       </c>
       <c r="W26" t="s">
+        <v>205</v>
+      </c>
+      <c r="X26" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z26" t="s">
         <v>209</v>
       </c>
-      <c r="X26" t="s">
+      <c r="AA26" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB26" t="s">
         <v>211</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="AC26" t="s">
         <v>212</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="AD26" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE26" t="s">
         <v>213</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB26" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC26" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE26" t="s">
-        <v>217</v>
       </c>
       <c r="AF26">
         <v>46635747000</v>
@@ -6104,42 +6089,42 @@
         <v>46635747000</v>
       </c>
       <c r="AH26" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI26" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ26" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK26" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B27" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C27" t="s">
         <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E27" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G27" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H27" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I27" t="s">
         <v>34</v>
@@ -6148,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L27" t="s">
         <v>15</v>
@@ -6157,22 +6142,22 @@
         <v>1171</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O27" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q27" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R27" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="S27" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T27">
         <v>-1295.8970000000002</v>
@@ -6187,28 +6172,28 @@
         <v>80000</v>
       </c>
       <c r="X27" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB27" t="s">
         <v>211</v>
       </c>
-      <c r="Y27" t="s">
+      <c r="AC27" t="s">
         <v>212</v>
       </c>
-      <c r="Z27" t="s">
+      <c r="AD27" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE27" t="s">
         <v>213</v>
-      </c>
-      <c r="AA27" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB27" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC27" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE27" t="s">
-        <v>217</v>
       </c>
       <c r="AF27">
         <v>300476914000</v>
@@ -6217,42 +6202,42 @@
         <v>300476914000</v>
       </c>
       <c r="AH27" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI27" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ27" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK27" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B28" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C28" t="s">
         <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H28" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I28" t="s">
         <v>34</v>
@@ -6261,7 +6246,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L28" t="s">
         <v>15</v>
@@ -6270,22 +6255,22 @@
         <v>712</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="O28" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q28" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R28" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S28" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T28">
         <v>-4.9999999999883471E-3</v>
@@ -6300,28 +6285,28 @@
         <v>70000</v>
       </c>
       <c r="X28" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB28" t="s">
         <v>211</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="AC28" t="s">
         <v>212</v>
       </c>
-      <c r="Z28" t="s">
+      <c r="AD28" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE28" t="s">
         <v>213</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB28" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE28" t="s">
-        <v>217</v>
       </c>
       <c r="AF28">
         <v>63529475000</v>
@@ -6330,42 +6315,42 @@
         <v>63529475000</v>
       </c>
       <c r="AH28" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI28" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ28" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK28" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B29" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C29" t="s">
         <v>21</v>
       </c>
       <c r="D29" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E29" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G29" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H29" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I29" t="s">
         <v>34</v>
@@ -6374,7 +6359,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L29" t="s">
         <v>15</v>
@@ -6383,22 +6368,22 @@
         <v>1171</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O29" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q29" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R29" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="S29" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T29">
         <v>-1305.7286575342464</v>
@@ -6413,28 +6398,28 @@
         <v>25000</v>
       </c>
       <c r="X29" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB29" t="s">
         <v>211</v>
       </c>
-      <c r="Y29" t="s">
+      <c r="AC29" t="s">
         <v>212</v>
       </c>
-      <c r="Z29" t="s">
+      <c r="AD29" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE29" t="s">
         <v>213</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB29" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE29" t="s">
-        <v>217</v>
       </c>
       <c r="AF29">
         <v>247725645000</v>
@@ -6443,42 +6428,42 @@
         <v>247725645000</v>
       </c>
       <c r="AH29" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI29" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ29" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK29" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B30" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C30" t="s">
         <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E30" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G30" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H30" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I30" t="s">
         <v>34</v>
@@ -6487,7 +6472,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L30" t="s">
         <v>15</v>
@@ -6496,22 +6481,22 @@
         <v>1171</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O30" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q30" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R30" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="S30" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T30">
         <v>-1311.9314794520546</v>
@@ -6523,31 +6508,31 @@
         <v>0</v>
       </c>
       <c r="W30" t="s">
+        <v>205</v>
+      </c>
+      <c r="X30" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z30" t="s">
         <v>209</v>
       </c>
-      <c r="X30" t="s">
+      <c r="AA30" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB30" t="s">
         <v>211</v>
       </c>
-      <c r="Y30" t="s">
+      <c r="AC30" t="s">
         <v>212</v>
       </c>
-      <c r="Z30" t="s">
+      <c r="AD30" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE30" t="s">
         <v>213</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB30" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>217</v>
       </c>
       <c r="AF30">
         <v>183966410000</v>
@@ -6556,42 +6541,42 @@
         <v>183966410000</v>
       </c>
       <c r="AH30" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI30" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK30" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B31" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E31" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G31" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H31" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I31" t="s">
         <v>14</v>
@@ -6600,7 +6585,7 @@
         <v>6</v>
       </c>
       <c r="K31" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L31" t="s">
         <v>19</v>
@@ -6609,19 +6594,19 @@
         <v>1193</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O31" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q31" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="R31" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S31">
         <v>2</v>
@@ -6636,31 +6621,31 @@
         <v>0</v>
       </c>
       <c r="W31" t="s">
+        <v>205</v>
+      </c>
+      <c r="X31" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z31" t="s">
         <v>209</v>
       </c>
-      <c r="X31" t="s">
+      <c r="AA31" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB31" t="s">
         <v>211</v>
       </c>
-      <c r="Y31" t="s">
+      <c r="AC31" t="s">
         <v>212</v>
       </c>
-      <c r="Z31" t="s">
+      <c r="AD31" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE31" t="s">
         <v>213</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB31" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC31" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE31" t="s">
-        <v>217</v>
       </c>
       <c r="AF31">
         <v>198749597000</v>
@@ -6669,42 +6654,42 @@
         <v>198749597000</v>
       </c>
       <c r="AH31" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI31" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ31" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK31" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B32" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C32" t="s">
         <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E32" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G32" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H32" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I32" t="s">
         <v>34</v>
@@ -6713,7 +6698,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L32" t="s">
         <v>15</v>
@@ -6722,22 +6707,22 @@
         <v>1171</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O32" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q32" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R32" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S32" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T32">
         <v>-1318.494301369863</v>
@@ -6749,31 +6734,31 @@
         <v>0</v>
       </c>
       <c r="W32" t="s">
+        <v>205</v>
+      </c>
+      <c r="X32" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z32" t="s">
         <v>209</v>
       </c>
-      <c r="X32" t="s">
+      <c r="AA32" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB32" t="s">
         <v>211</v>
       </c>
-      <c r="Y32" t="s">
+      <c r="AC32" t="s">
         <v>212</v>
       </c>
-      <c r="Z32" t="s">
+      <c r="AD32" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE32" t="s">
         <v>213</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB32" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE32" t="s">
-        <v>217</v>
       </c>
       <c r="AF32">
         <v>201665761000</v>
@@ -6782,42 +6767,42 @@
         <v>201665761000</v>
       </c>
       <c r="AH32" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI32" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ32" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK32" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B33" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C33" t="s">
         <v>21</v>
       </c>
       <c r="D33" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E33" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G33" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H33" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I33" t="s">
         <v>34</v>
@@ -6826,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L33" t="s">
         <v>15</v>
@@ -6835,22 +6820,22 @@
         <v>1171</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O33" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q33" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R33" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S33" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="T33">
         <v>-1324.9650273972604</v>
@@ -6865,28 +6850,28 @@
         <v>95000</v>
       </c>
       <c r="X33" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB33" t="s">
         <v>211</v>
       </c>
-      <c r="Y33" t="s">
+      <c r="AC33" t="s">
         <v>212</v>
       </c>
-      <c r="Z33" t="s">
+      <c r="AD33" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE33" t="s">
         <v>213</v>
-      </c>
-      <c r="AA33" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB33" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC33" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD33" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE33" t="s">
-        <v>217</v>
       </c>
       <c r="AF33">
         <v>133532576000</v>
@@ -6895,268 +6880,268 @@
         <v>133532576000</v>
       </c>
       <c r="AH33" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI33" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ33" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK33" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B34" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C34" t="s">
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="G34" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H34" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I34" t="s">
         <v>14</v>
       </c>
       <c r="J34">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K34" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L34" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M34">
-        <v>1195</v>
+        <v>1309</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O34" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="Q34" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="R34" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S34">
         <v>2</v>
       </c>
       <c r="T34">
-        <v>-539.62000000000069</v>
+        <v>-9.9999999992661515E-3</v>
       </c>
       <c r="U34">
-        <v>7.9775</v>
+        <v>13.3736</v>
       </c>
       <c r="V34">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="W34">
-        <v>113646</v>
+        <v>3476761</v>
       </c>
       <c r="X34" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB34" t="s">
         <v>211</v>
       </c>
-      <c r="Y34" t="s">
+      <c r="AC34" t="s">
         <v>212</v>
       </c>
-      <c r="Z34" t="s">
+      <c r="AD34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE34" t="s">
         <v>213</v>
       </c>
-      <c r="AA34" t="s">
+      <c r="AF34">
+        <v>144593286000</v>
+      </c>
+      <c r="AG34">
+        <v>144593286000</v>
+      </c>
+      <c r="AH34" t="s">
         <v>214</v>
       </c>
-      <c r="AB34" t="s">
+      <c r="AI34" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ34" t="s">
         <v>215</v>
       </c>
-      <c r="AC34" t="s">
+      <c r="AK34" t="s">
         <v>216</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE34" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF34">
-        <v>102743024000</v>
-      </c>
-      <c r="AG34">
-        <v>102743024000</v>
-      </c>
-      <c r="AH34" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI34" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ34" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK34" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D35" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E35" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s">
-        <v>275</v>
+        <v>83</v>
       </c>
       <c r="H35" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I35" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="J35">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L35" t="s">
         <v>15</v>
       </c>
       <c r="M35">
-        <v>1309</v>
+        <v>1171</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="O35" t="s">
+        <v>203</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>205</v>
+      </c>
+      <c r="R35" t="s">
+        <v>223</v>
+      </c>
+      <c r="S35" t="s">
+        <v>203</v>
+      </c>
+      <c r="T35">
+        <v>-1328.9425205479454</v>
+      </c>
+      <c r="U35">
+        <v>0.1017</v>
+      </c>
+      <c r="V35">
+        <v>1</v>
+      </c>
+      <c r="W35">
+        <v>25000</v>
+      </c>
+      <c r="X35" t="s">
         <v>207</v>
       </c>
-      <c r="P35" s="3" t="s">
+      <c r="Y35" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z35" t="s">
         <v>209</v>
       </c>
-      <c r="Q35" t="s">
-        <v>209</v>
-      </c>
-      <c r="R35" t="s">
-        <v>227</v>
-      </c>
-      <c r="S35">
-        <v>2</v>
-      </c>
-      <c r="T35">
-        <v>-9.9999999992661515E-3</v>
-      </c>
-      <c r="U35">
-        <v>13.3736</v>
-      </c>
-      <c r="V35">
-        <v>14</v>
-      </c>
-      <c r="W35">
-        <v>3476761</v>
-      </c>
-      <c r="X35" t="s">
+      <c r="AA35" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB35" t="s">
         <v>211</v>
       </c>
-      <c r="Y35" t="s">
+      <c r="AC35" t="s">
         <v>212</v>
       </c>
-      <c r="Z35" t="s">
+      <c r="AD35" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE35" t="s">
         <v>213</v>
       </c>
-      <c r="AA35" t="s">
+      <c r="AF35">
+        <v>175399627000</v>
+      </c>
+      <c r="AG35">
+        <v>175399627000</v>
+      </c>
+      <c r="AH35" t="s">
         <v>214</v>
       </c>
-      <c r="AB35" t="s">
+      <c r="AI35" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ35" t="s">
         <v>215</v>
       </c>
-      <c r="AC35" t="s">
+      <c r="AK35" t="s">
         <v>216</v>
-      </c>
-      <c r="AD35" t="s">
-        <v>127</v>
-      </c>
-      <c r="AE35" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF35">
-        <v>144593286000</v>
-      </c>
-      <c r="AG35">
-        <v>144593286000</v>
-      </c>
-      <c r="AH35" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI35" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ35" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK35" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C36" t="s">
         <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E36" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H36" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I36" t="s">
         <v>34</v>
@@ -7165,7 +7150,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L36" t="s">
         <v>15</v>
@@ -7174,90 +7159,90 @@
         <v>1171</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O36" t="s">
+        <v>203</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>205</v>
+      </c>
+      <c r="R36" t="s">
+        <v>223</v>
+      </c>
+      <c r="S36" t="s">
+        <v>203</v>
+      </c>
+      <c r="T36">
+        <v>-1331.6796712328769</v>
+      </c>
+      <c r="U36">
+        <v>0.10150000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36" t="s">
+        <v>205</v>
+      </c>
+      <c r="X36" t="s">
         <v>207</v>
       </c>
-      <c r="P36" s="3" t="s">
+      <c r="Y36" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z36" t="s">
         <v>209</v>
       </c>
-      <c r="Q36" t="s">
-        <v>209</v>
-      </c>
-      <c r="R36" t="s">
-        <v>227</v>
-      </c>
-      <c r="S36" t="s">
-        <v>207</v>
-      </c>
-      <c r="T36">
-        <v>-1328.9425205479454</v>
-      </c>
-      <c r="U36">
-        <v>0.1017</v>
-      </c>
-      <c r="V36">
-        <v>1</v>
-      </c>
-      <c r="W36">
-        <v>25000</v>
-      </c>
-      <c r="X36" t="s">
+      <c r="AA36" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB36" t="s">
         <v>211</v>
       </c>
-      <c r="Y36" t="s">
+      <c r="AC36" t="s">
         <v>212</v>
       </c>
-      <c r="Z36" t="s">
+      <c r="AD36" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE36" t="s">
         <v>213</v>
       </c>
-      <c r="AA36" t="s">
+      <c r="AF36">
+        <v>174919327000</v>
+      </c>
+      <c r="AG36">
+        <v>174919327000</v>
+      </c>
+      <c r="AH36" t="s">
         <v>214</v>
       </c>
-      <c r="AB36" t="s">
+      <c r="AI36" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ36" t="s">
         <v>215</v>
       </c>
-      <c r="AC36" t="s">
+      <c r="AK36" t="s">
         <v>216</v>
-      </c>
-      <c r="AD36" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE36" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF36">
-        <v>175399627000</v>
-      </c>
-      <c r="AG36">
-        <v>175399627000</v>
-      </c>
-      <c r="AH36" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI36" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ36" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK36" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B37" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C37" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D37" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E37" t="s">
         <v>77</v>
@@ -7266,10 +7251,10 @@
         <v>78</v>
       </c>
       <c r="G37" t="s">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="H37" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I37" t="s">
         <v>34</v>
@@ -7278,676 +7263,676 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L37" t="s">
         <v>15</v>
       </c>
       <c r="M37">
-        <v>1171</v>
+        <v>712</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="O37" t="s">
+        <v>203</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>205</v>
+      </c>
+      <c r="R37" t="s">
+        <v>223</v>
+      </c>
+      <c r="S37" t="s">
+        <v>203</v>
+      </c>
+      <c r="T37">
+        <v>-9.9999999999766942E-3</v>
+      </c>
+      <c r="U37">
+        <v>13.481400000000001</v>
+      </c>
+      <c r="V37">
+        <v>2</v>
+      </c>
+      <c r="W37">
+        <v>90000</v>
+      </c>
+      <c r="X37" t="s">
         <v>207</v>
       </c>
-      <c r="P37" s="3" t="s">
+      <c r="Y37" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z37" t="s">
         <v>209</v>
       </c>
-      <c r="Q37" t="s">
-        <v>209</v>
-      </c>
-      <c r="R37" t="s">
-        <v>227</v>
-      </c>
-      <c r="S37" t="s">
-        <v>207</v>
-      </c>
-      <c r="T37">
-        <v>-1331.6796712328769</v>
-      </c>
-      <c r="U37">
-        <v>0.10150000000000001</v>
-      </c>
-      <c r="V37">
-        <v>0</v>
-      </c>
-      <c r="W37" t="s">
-        <v>209</v>
-      </c>
-      <c r="X37" t="s">
+      <c r="AA37" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB37" t="s">
         <v>211</v>
       </c>
-      <c r="Y37" t="s">
+      <c r="AC37" t="s">
         <v>212</v>
       </c>
-      <c r="Z37" t="s">
+      <c r="AD37" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE37" t="s">
         <v>213</v>
       </c>
-      <c r="AA37" t="s">
+      <c r="AF37">
+        <v>67998267000</v>
+      </c>
+      <c r="AG37">
+        <v>67998267000</v>
+      </c>
+      <c r="AH37" t="s">
         <v>214</v>
       </c>
-      <c r="AB37" t="s">
+      <c r="AI37" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ37" t="s">
         <v>215</v>
       </c>
-      <c r="AC37" t="s">
+      <c r="AK37" t="s">
         <v>216</v>
-      </c>
-      <c r="AD37" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE37" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF37">
-        <v>174919327000</v>
-      </c>
-      <c r="AG37">
-        <v>174919327000</v>
-      </c>
-      <c r="AH37" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI37" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ37" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK37" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E38" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G38" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H38" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I38" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K38" t="s">
+        <v>203</v>
+      </c>
+      <c r="L38" t="s">
+        <v>19</v>
+      </c>
+      <c r="M38">
+        <v>1193</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="O38" t="s">
+        <v>203</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>205</v>
+      </c>
+      <c r="R38" t="s">
+        <v>223</v>
+      </c>
+      <c r="S38">
+        <v>2</v>
+      </c>
+      <c r="T38">
+        <v>-4.9999999996330757E-3</v>
+      </c>
+      <c r="U38">
+        <v>7.6054000000000004</v>
+      </c>
+      <c r="V38" t="s">
+        <v>205</v>
+      </c>
+      <c r="W38" t="s">
+        <v>205</v>
+      </c>
+      <c r="X38" t="s">
         <v>207</v>
       </c>
-      <c r="L38" t="s">
-        <v>15</v>
-      </c>
-      <c r="M38">
-        <v>712</v>
-      </c>
-      <c r="N38" s="4" t="s">
+      <c r="Y38" t="s">
         <v>208</v>
       </c>
-      <c r="O38" t="s">
-        <v>207</v>
-      </c>
-      <c r="P38" s="3" t="s">
+      <c r="Z38" t="s">
         <v>209</v>
       </c>
-      <c r="Q38" t="s">
-        <v>209</v>
-      </c>
-      <c r="R38" t="s">
-        <v>227</v>
-      </c>
-      <c r="S38" t="s">
-        <v>207</v>
-      </c>
-      <c r="T38">
-        <v>-9.9999999999766942E-3</v>
-      </c>
-      <c r="U38">
-        <v>13.481400000000001</v>
-      </c>
-      <c r="V38">
-        <v>2</v>
-      </c>
-      <c r="W38">
-        <v>90000</v>
-      </c>
-      <c r="X38" t="s">
+      <c r="AA38" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB38" t="s">
         <v>211</v>
       </c>
-      <c r="Y38" t="s">
+      <c r="AC38" t="s">
         <v>212</v>
       </c>
-      <c r="Z38" t="s">
+      <c r="AD38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE38" t="s">
         <v>213</v>
       </c>
-      <c r="AA38" t="s">
+      <c r="AF38">
+        <v>103089325000</v>
+      </c>
+      <c r="AG38">
+        <v>103089325000</v>
+      </c>
+      <c r="AH38" t="s">
         <v>214</v>
       </c>
-      <c r="AB38" t="s">
+      <c r="AI38" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ38" t="s">
         <v>215</v>
       </c>
-      <c r="AC38" t="s">
+      <c r="AK38" t="s">
         <v>216</v>
-      </c>
-      <c r="AD38" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE38" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF38">
-        <v>67998267000</v>
-      </c>
-      <c r="AG38">
-        <v>67998267000</v>
-      </c>
-      <c r="AH38" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI38" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ38" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK38" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="39" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E39" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G39" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="H39" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I39" t="s">
         <v>14</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K39" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L39" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M39">
-        <v>1193</v>
+        <v>1309</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O39" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q39" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R39" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S39">
         <v>2</v>
       </c>
       <c r="T39">
-        <v>-4.9999999996330757E-3</v>
+        <v>-4.99999999945544E-3</v>
       </c>
       <c r="U39">
-        <v>7.6054000000000004</v>
-      </c>
-      <c r="V39" t="s">
+        <v>13.584</v>
+      </c>
+      <c r="V39">
+        <v>1</v>
+      </c>
+      <c r="W39">
+        <v>127000</v>
+      </c>
+      <c r="X39" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z39" t="s">
         <v>209</v>
       </c>
-      <c r="W39" t="s">
-        <v>209</v>
-      </c>
-      <c r="X39" t="s">
+      <c r="AA39" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB39" t="s">
         <v>211</v>
       </c>
-      <c r="Y39" t="s">
+      <c r="AC39" t="s">
         <v>212</v>
       </c>
-      <c r="Z39" t="s">
+      <c r="AD39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE39" t="s">
         <v>213</v>
       </c>
-      <c r="AA39" t="s">
+      <c r="AF39">
+        <v>48858398000</v>
+      </c>
+      <c r="AG39">
+        <v>48858398000</v>
+      </c>
+      <c r="AH39" t="s">
         <v>214</v>
       </c>
-      <c r="AB39" t="s">
+      <c r="AI39" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ39" t="s">
         <v>215</v>
       </c>
-      <c r="AC39" t="s">
+      <c r="AK39" t="s">
         <v>216</v>
-      </c>
-      <c r="AD39" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE39" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF39">
-        <v>103089325000</v>
-      </c>
-      <c r="AG39">
-        <v>103089325000</v>
-      </c>
-      <c r="AH39" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI39" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ39" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK39" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="40" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B40" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E40" t="s">
-        <v>38</v>
+        <v>116</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>33</v>
+        <v>117</v>
       </c>
       <c r="G40" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H40" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I40" t="s">
         <v>14</v>
       </c>
       <c r="J40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K40" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L40" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M40">
-        <v>1309</v>
+        <v>1193</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="O40" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q40" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R40" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S40">
         <v>2</v>
       </c>
       <c r="T40">
-        <v>-4.99999999945544E-3</v>
+        <v>-9.9999999991773336E-3</v>
       </c>
       <c r="U40">
-        <v>13.584</v>
+        <v>7.5644</v>
       </c>
       <c r="V40">
-        <v>1</v>
-      </c>
-      <c r="W40">
-        <v>127000</v>
+        <v>0</v>
+      </c>
+      <c r="W40" t="s">
+        <v>205</v>
       </c>
       <c r="X40" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB40" t="s">
         <v>211</v>
       </c>
-      <c r="Y40" t="s">
+      <c r="AC40" t="s">
         <v>212</v>
       </c>
-      <c r="Z40" t="s">
+      <c r="AD40" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE40" t="s">
         <v>213</v>
       </c>
-      <c r="AA40" t="s">
+      <c r="AF40">
+        <v>50523297000</v>
+      </c>
+      <c r="AG40">
+        <v>50523297000</v>
+      </c>
+      <c r="AH40" t="s">
         <v>214</v>
       </c>
-      <c r="AB40" t="s">
+      <c r="AI40" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ40" t="s">
         <v>215</v>
       </c>
-      <c r="AC40" t="s">
+      <c r="AK40" t="s">
         <v>216</v>
-      </c>
-      <c r="AD40" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE40" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF40">
-        <v>48858398000</v>
-      </c>
-      <c r="AG40">
-        <v>48858398000</v>
-      </c>
-      <c r="AH40" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI40" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK40" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="41" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B41" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C41" t="s">
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E41" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="G41" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H41" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I41" t="s">
         <v>14</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K41" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L41" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M41">
-        <v>1193</v>
+        <v>1309</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O41" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q41" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R41" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S41">
         <v>2</v>
       </c>
       <c r="T41">
-        <v>-9.9999999991773336E-3</v>
+        <v>-4.9999999985672616E-3</v>
       </c>
       <c r="U41">
-        <v>7.5644</v>
+        <v>13.669700000000001</v>
       </c>
       <c r="V41">
-        <v>0</v>
-      </c>
-      <c r="W41" t="s">
+        <v>7</v>
+      </c>
+      <c r="W41">
+        <v>153459000</v>
+      </c>
+      <c r="X41" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z41" t="s">
         <v>209</v>
       </c>
-      <c r="X41" t="s">
+      <c r="AA41" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB41" t="s">
         <v>211</v>
       </c>
-      <c r="Y41" t="s">
+      <c r="AC41" t="s">
         <v>212</v>
       </c>
-      <c r="Z41" t="s">
+      <c r="AD41" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE41" t="s">
         <v>213</v>
       </c>
-      <c r="AA41" t="s">
+      <c r="AF41">
+        <v>94853477000</v>
+      </c>
+      <c r="AG41">
+        <v>94853477000</v>
+      </c>
+      <c r="AH41" t="s">
         <v>214</v>
       </c>
-      <c r="AB41" t="s">
+      <c r="AI41" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ41" t="s">
         <v>215</v>
       </c>
-      <c r="AC41" t="s">
+      <c r="AK41" t="s">
         <v>216</v>
-      </c>
-      <c r="AD41" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE41" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF41">
-        <v>50523297000</v>
-      </c>
-      <c r="AG41">
-        <v>50523297000</v>
-      </c>
-      <c r="AH41" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI41" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ41" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK41" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B42" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E42" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="G42" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H42" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I42" t="s">
         <v>14</v>
       </c>
       <c r="J42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K42" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L42" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M42">
-        <v>1309</v>
+        <v>1193</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="O42" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="Q42" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="R42" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S42">
         <v>2</v>
       </c>
       <c r="T42">
-        <v>-4.9999999985672616E-3</v>
+        <v>-1.0000000000331966E-2</v>
       </c>
       <c r="U42">
-        <v>13.669700000000001</v>
+        <v>7.4120999999999997</v>
       </c>
       <c r="V42">
-        <v>7</v>
-      </c>
-      <c r="W42">
-        <v>153459000</v>
+        <v>0</v>
+      </c>
+      <c r="W42" t="s">
+        <v>205</v>
       </c>
       <c r="X42" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB42" t="s">
         <v>211</v>
       </c>
-      <c r="Y42" t="s">
+      <c r="AC42" t="s">
         <v>212</v>
       </c>
-      <c r="Z42" t="s">
+      <c r="AD42" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE42" t="s">
         <v>213</v>
       </c>
-      <c r="AA42" t="s">
+      <c r="AF42">
+        <v>227460819000</v>
+      </c>
+      <c r="AG42">
+        <v>227460819000</v>
+      </c>
+      <c r="AH42" t="s">
         <v>214</v>
       </c>
-      <c r="AB42" t="s">
+      <c r="AI42" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ42" t="s">
         <v>215</v>
       </c>
-      <c r="AC42" t="s">
+      <c r="AK42" t="s">
         <v>216</v>
-      </c>
-      <c r="AD42" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE42" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF42">
-        <v>94853477000</v>
-      </c>
-      <c r="AG42">
-        <v>94853477000</v>
-      </c>
-      <c r="AH42" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI42" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ42" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK42" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="43" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B43" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C43" t="s">
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E43" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G43" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H43" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I43" t="s">
         <v>14</v>
@@ -7956,7 +7941,7 @@
         <v>6</v>
       </c>
       <c r="K43" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L43" t="s">
         <v>19</v>
@@ -7965,102 +7950,102 @@
         <v>1193</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O43" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q43" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="R43" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S43">
         <v>2</v>
       </c>
       <c r="T43">
-        <v>-1.0000000000331966E-2</v>
+        <v>-1.0000000000243148E-2</v>
       </c>
       <c r="U43">
-        <v>7.4120999999999997</v>
+        <v>7.2404999999999999</v>
       </c>
       <c r="V43">
         <v>0</v>
       </c>
       <c r="W43" t="s">
+        <v>205</v>
+      </c>
+      <c r="X43" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z43" t="s">
         <v>209</v>
       </c>
-      <c r="X43" t="s">
+      <c r="AA43" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB43" t="s">
         <v>211</v>
       </c>
-      <c r="Y43" t="s">
+      <c r="AC43" t="s">
         <v>212</v>
-      </c>
-      <c r="Z43" t="s">
-        <v>213</v>
-      </c>
-      <c r="AA43" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB43" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC43" t="s">
-        <v>216</v>
       </c>
       <c r="AD43" t="s">
         <v>62</v>
       </c>
       <c r="AE43" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AF43">
-        <v>227460819000</v>
+        <v>113614908000</v>
       </c>
       <c r="AG43">
-        <v>227460819000</v>
+        <v>113614908000</v>
       </c>
       <c r="AH43" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AI43" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AJ43" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK43" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B44" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E44" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G44" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H44" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I44" t="s">
         <v>14</v>
@@ -8069,7 +8054,7 @@
         <v>6</v>
       </c>
       <c r="K44" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L44" t="s">
         <v>19</v>
@@ -8078,102 +8063,102 @@
         <v>1193</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O44" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q44" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="R44" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S44">
         <v>2</v>
       </c>
       <c r="T44">
-        <v>-1.0000000000243148E-2</v>
+        <v>-9.9999999991773336E-3</v>
       </c>
       <c r="U44">
-        <v>7.2404999999999999</v>
+        <v>7.1605999999999996</v>
       </c>
       <c r="V44">
         <v>0</v>
       </c>
       <c r="W44" t="s">
+        <v>205</v>
+      </c>
+      <c r="X44" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z44" t="s">
         <v>209</v>
       </c>
-      <c r="X44" t="s">
+      <c r="AA44" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB44" t="s">
         <v>211</v>
       </c>
-      <c r="Y44" t="s">
+      <c r="AC44" t="s">
         <v>212</v>
       </c>
-      <c r="Z44" t="s">
+      <c r="AD44" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE44" t="s">
         <v>213</v>
       </c>
-      <c r="AA44" t="s">
+      <c r="AF44">
+        <v>154923814000</v>
+      </c>
+      <c r="AG44">
+        <v>154923814000</v>
+      </c>
+      <c r="AH44" t="s">
         <v>214</v>
       </c>
-      <c r="AB44" t="s">
+      <c r="AI44" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ44" t="s">
         <v>215</v>
       </c>
-      <c r="AC44" t="s">
+      <c r="AK44" t="s">
         <v>216</v>
-      </c>
-      <c r="AD44" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE44" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF44">
-        <v>113614908000</v>
-      </c>
-      <c r="AG44">
-        <v>113614908000</v>
-      </c>
-      <c r="AH44" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI44" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ44" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK44" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="45" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B45" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C45" t="s">
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G45" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H45" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I45" t="s">
         <v>14</v>
@@ -8182,7 +8167,7 @@
         <v>6</v>
       </c>
       <c r="K45" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L45" t="s">
         <v>19</v>
@@ -8191,102 +8176,102 @@
         <v>1193</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O45" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q45" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="R45" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S45">
         <v>2</v>
       </c>
       <c r="T45">
-        <v>-9.9999999991773336E-3</v>
+        <v>-9.9999999981115195E-3</v>
       </c>
       <c r="U45">
-        <v>7.1605999999999996</v>
+        <v>7.0641999999999996</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45" t="s">
+        <v>205</v>
+      </c>
+      <c r="X45" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z45" t="s">
         <v>209</v>
       </c>
-      <c r="X45" t="s">
+      <c r="AA45" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB45" t="s">
         <v>211</v>
       </c>
-      <c r="Y45" t="s">
+      <c r="AC45" t="s">
         <v>212</v>
       </c>
-      <c r="Z45" t="s">
+      <c r="AD45" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE45" t="s">
         <v>213</v>
       </c>
-      <c r="AA45" t="s">
+      <c r="AF45">
+        <v>187555521000</v>
+      </c>
+      <c r="AG45">
+        <v>187555521000</v>
+      </c>
+      <c r="AH45" t="s">
         <v>214</v>
       </c>
-      <c r="AB45" t="s">
+      <c r="AI45" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ45" t="s">
         <v>215</v>
       </c>
-      <c r="AC45" t="s">
+      <c r="AK45" t="s">
         <v>216</v>
-      </c>
-      <c r="AD45" t="s">
-        <v>59</v>
-      </c>
-      <c r="AE45" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF45">
-        <v>154923814000</v>
-      </c>
-      <c r="AG45">
-        <v>154923814000</v>
-      </c>
-      <c r="AH45" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI45" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ45" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK45" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="46" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B46" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E46" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G46" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="H46" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I46" t="s">
         <v>14</v>
@@ -8295,7 +8280,7 @@
         <v>6</v>
       </c>
       <c r="K46" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L46" t="s">
         <v>19</v>
@@ -8304,102 +8289,102 @@
         <v>1193</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O46" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q46" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="R46" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="S46">
         <v>2</v>
       </c>
       <c r="T46">
-        <v>-9.9999999981115195E-3</v>
+        <v>-4.9999999996330757E-3</v>
       </c>
       <c r="U46">
-        <v>7.0641999999999996</v>
+        <v>7.0522999999999998</v>
       </c>
       <c r="V46">
         <v>0</v>
       </c>
       <c r="W46" t="s">
+        <v>205</v>
+      </c>
+      <c r="X46" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z46" t="s">
         <v>209</v>
       </c>
-      <c r="X46" t="s">
+      <c r="AA46" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB46" t="s">
         <v>211</v>
       </c>
-      <c r="Y46" t="s">
+      <c r="AC46" t="s">
         <v>212</v>
       </c>
-      <c r="Z46" t="s">
+      <c r="AD46" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE46" t="s">
         <v>213</v>
       </c>
-      <c r="AA46" t="s">
+      <c r="AF46">
+        <v>122303590000</v>
+      </c>
+      <c r="AG46">
+        <v>122303590000</v>
+      </c>
+      <c r="AH46" t="s">
         <v>214</v>
       </c>
-      <c r="AB46" t="s">
+      <c r="AI46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ46" t="s">
         <v>215</v>
       </c>
-      <c r="AC46" t="s">
+      <c r="AK46" t="s">
         <v>216</v>
-      </c>
-      <c r="AD46" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE46" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF46">
-        <v>187555521000</v>
-      </c>
-      <c r="AG46">
-        <v>187555521000</v>
-      </c>
-      <c r="AH46" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI46" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ46" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK46" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="47" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B47" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C47" t="s">
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E47" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="G47" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H47" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I47" t="s">
         <v>14</v>
@@ -8408,7 +8393,7 @@
         <v>6</v>
       </c>
       <c r="K47" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L47" t="s">
         <v>19</v>
@@ -8417,203 +8402,91 @@
         <v>1193</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O47" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="Q47" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="R47" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="S47">
         <v>2</v>
       </c>
       <c r="T47">
-        <v>-4.9999999996330757E-3</v>
+        <v>-1.000000000139778E-2</v>
       </c>
       <c r="U47">
-        <v>7.0522999999999998</v>
+        <v>7.0503999999999998</v>
       </c>
       <c r="V47">
         <v>0</v>
       </c>
       <c r="W47" t="s">
+        <v>205</v>
+      </c>
+      <c r="X47" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z47" t="s">
         <v>209</v>
       </c>
-      <c r="X47" t="s">
+      <c r="AA47" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB47" t="s">
         <v>211</v>
       </c>
-      <c r="Y47" t="s">
+      <c r="AC47" t="s">
         <v>212</v>
       </c>
-      <c r="Z47" t="s">
+      <c r="AD47" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE47" t="s">
         <v>213</v>
       </c>
-      <c r="AA47" t="s">
+      <c r="AF47">
+        <v>83659321000</v>
+      </c>
+      <c r="AG47">
+        <v>83659321000</v>
+      </c>
+      <c r="AH47" t="s">
         <v>214</v>
       </c>
-      <c r="AB47" t="s">
+      <c r="AI47" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ47" t="s">
         <v>215</v>
       </c>
-      <c r="AC47" t="s">
+      <c r="AK47" t="s">
         <v>216</v>
       </c>
-      <c r="AD47" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE47" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF47">
-        <v>122303590000</v>
-      </c>
-      <c r="AG47">
-        <v>122303590000</v>
-      </c>
-      <c r="AH47" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI47" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ47" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK47" t="s">
-        <v>220</v>
-      </c>
     </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>179</v>
-      </c>
-      <c r="B48" t="s">
-        <v>179</v>
-      </c>
-      <c r="C48" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" t="s">
-        <v>299</v>
-      </c>
-      <c r="E48" t="s">
-        <v>45</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G48" t="s">
-        <v>300</v>
-      </c>
-      <c r="H48" t="s">
-        <v>206</v>
-      </c>
-      <c r="I48" t="s">
-        <v>14</v>
-      </c>
-      <c r="J48">
-        <v>6</v>
-      </c>
-      <c r="K48" t="s">
-        <v>207</v>
-      </c>
-      <c r="L48" t="s">
-        <v>19</v>
-      </c>
-      <c r="M48">
-        <v>1193</v>
-      </c>
-      <c r="N48" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="O48" t="s">
-        <v>207</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>209</v>
-      </c>
-      <c r="R48" t="s">
-        <v>227</v>
-      </c>
-      <c r="S48">
-        <v>2</v>
-      </c>
-      <c r="T48">
-        <v>-1.000000000139778E-2</v>
-      </c>
-      <c r="U48">
-        <v>7.0503999999999998</v>
-      </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-      <c r="W48" t="s">
-        <v>209</v>
-      </c>
-      <c r="X48" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y48" t="s">
-        <v>212</v>
-      </c>
-      <c r="Z48" t="s">
-        <v>213</v>
-      </c>
-      <c r="AA48" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB48" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC48" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD48" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE48" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF48">
-        <v>83659321000</v>
-      </c>
-      <c r="AG48">
-        <v>83659321000</v>
-      </c>
-      <c r="AH48" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI48" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ48" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK48" t="s">
-        <v>220</v>
-      </c>
+    <row r="51" spans="13:17" x14ac:dyDescent="0.35">
+      <c r="Q51" s="2"/>
     </row>
-    <row r="52" spans="13:17" x14ac:dyDescent="0.35">
-      <c r="Q52" s="2"/>
+    <row r="56" spans="13:17" x14ac:dyDescent="0.35">
+      <c r="M56" s="3"/>
     </row>
     <row r="57" spans="13:17" x14ac:dyDescent="0.35">
       <c r="M57" s="3"/>
     </row>
-    <row r="58" spans="13:17" x14ac:dyDescent="0.35">
-      <c r="M58" s="3"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:M48">
-    <sortCondition ref="F2:F48"/>
+  <autoFilter ref="A1:AK47" xr:uid="{A970A97D-4899-4477-842A-DD8D42C7E015}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:M47">
+    <sortCondition ref="F2:F47"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
